--- a/Cambium_Import_Details.xlsx
+++ b/Cambium_Import_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\czad\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73996E66-ADD3-48FC-BA31-EA937A412FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A4C236-A017-4ECE-8892-53621287C56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{42E993CD-9B70-4509-B668-6EEF51FEBD70}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="1213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="1230">
   <si>
     <t>SR NO</t>
   </si>
@@ -3696,6 +3696,57 @@
   </si>
   <si>
     <t>B0GN86G345</t>
+  </si>
+  <si>
+    <t>B0GW8Z556N</t>
+  </si>
+  <si>
+    <t>B0GW8VBCBL</t>
+  </si>
+  <si>
+    <t>B0GW9461N5</t>
+  </si>
+  <si>
+    <t>B0GW8YC59C</t>
+  </si>
+  <si>
+    <t>B0GW92TVVC</t>
+  </si>
+  <si>
+    <t>B0GW8XGPB2</t>
+  </si>
+  <si>
+    <t>B0GW92TQGV</t>
+  </si>
+  <si>
+    <t>B0GW96SHSK</t>
+  </si>
+  <si>
+    <t>B0GW92TTMS</t>
+  </si>
+  <si>
+    <t>B0GW92316G</t>
+  </si>
+  <si>
+    <t>B0GW96CQMG</t>
+  </si>
+  <si>
+    <t>B0GW8R2RYM</t>
+  </si>
+  <si>
+    <t>B0GW8ZQRFK</t>
+  </si>
+  <si>
+    <t>B0GTZND3ZN</t>
+  </si>
+  <si>
+    <t>B0GTZJF142</t>
+  </si>
+  <si>
+    <t>B0GTZLGPFR</t>
+  </si>
+  <si>
+    <t>B0GTZ9X8Q2</t>
   </si>
 </sst>
 </file>
@@ -3805,7 +3856,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3827,6 +3878,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3835,6 +3889,16 @@
   <dxfs count="196">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -3847,6 +3911,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -3919,6 +4003,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4003,6 +4107,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4027,66 +4141,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4099,6 +4153,56 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4161,16 +4265,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4215,46 +4309,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4339,6 +4393,66 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4363,96 +4477,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4495,6 +4519,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4519,6 +4573,66 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4571,26 +4685,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4638,6 +4732,356 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
@@ -4659,366 +5103,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -5729,36 +5813,6 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -10042,10 +10096,10 @@
         <v>413</v>
       </c>
       <c r="F137" s="7">
-        <v>0</v>
+        <v>522</v>
       </c>
       <c r="G137" s="8">
-        <v>1994</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -10686,10 +10740,10 @@
         <v>497</v>
       </c>
       <c r="F165" s="7">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="G165" s="8">
-        <v>1002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -15713,7 +15767,9 @@
       <c r="C384" s="4" t="s">
         <v>1170</v>
       </c>
-      <c r="D384" s="3"/>
+      <c r="D384" s="9" t="s">
+        <v>1213</v>
+      </c>
       <c r="E384" s="4" t="s">
         <v>1153</v>
       </c>
@@ -15734,7 +15790,9 @@
       <c r="C385" s="4" t="s">
         <v>1171</v>
       </c>
-      <c r="D385" s="3"/>
+      <c r="D385" s="9" t="s">
+        <v>1214</v>
+      </c>
       <c r="E385" s="4" t="s">
         <v>1154</v>
       </c>
@@ -15755,7 +15813,9 @@
       <c r="C386" s="4" t="s">
         <v>1172</v>
       </c>
-      <c r="D386" s="3"/>
+      <c r="D386" s="9" t="s">
+        <v>1215</v>
+      </c>
       <c r="E386" s="4" t="s">
         <v>1155</v>
       </c>
@@ -15776,7 +15836,9 @@
       <c r="C387" s="4" t="s">
         <v>1173</v>
       </c>
-      <c r="D387" s="3"/>
+      <c r="D387" s="9" t="s">
+        <v>1216</v>
+      </c>
       <c r="E387" s="4" t="s">
         <v>1156</v>
       </c>
@@ -15797,7 +15859,9 @@
       <c r="C388" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="D388" s="3"/>
+      <c r="D388" s="9" t="s">
+        <v>1217</v>
+      </c>
       <c r="E388" s="4" t="s">
         <v>1157</v>
       </c>
@@ -15818,7 +15882,9 @@
       <c r="C389" s="4" t="s">
         <v>1175</v>
       </c>
-      <c r="D389" s="3"/>
+      <c r="D389" s="9" t="s">
+        <v>1218</v>
+      </c>
       <c r="E389" s="4" t="s">
         <v>1158</v>
       </c>
@@ -15839,7 +15905,9 @@
       <c r="C390" s="4" t="s">
         <v>1176</v>
       </c>
-      <c r="D390" s="3"/>
+      <c r="D390" s="9" t="s">
+        <v>1219</v>
+      </c>
       <c r="E390" s="4" t="s">
         <v>1159</v>
       </c>
@@ -15860,7 +15928,9 @@
       <c r="C391" s="4" t="s">
         <v>1177</v>
       </c>
-      <c r="D391" s="3"/>
+      <c r="D391" s="9" t="s">
+        <v>1220</v>
+      </c>
       <c r="E391" s="4" t="s">
         <v>1160</v>
       </c>
@@ -15881,7 +15951,9 @@
       <c r="C392" s="4" t="s">
         <v>1178</v>
       </c>
-      <c r="D392" s="3"/>
+      <c r="D392" s="9" t="s">
+        <v>1221</v>
+      </c>
       <c r="E392" s="4" t="s">
         <v>1161</v>
       </c>
@@ -15902,7 +15974,9 @@
       <c r="C393" s="4" t="s">
         <v>1179</v>
       </c>
-      <c r="D393" s="3"/>
+      <c r="D393" s="9" t="s">
+        <v>1222</v>
+      </c>
       <c r="E393" s="4" t="s">
         <v>1162</v>
       </c>
@@ -15923,7 +15997,9 @@
       <c r="C394" s="4" t="s">
         <v>1180</v>
       </c>
-      <c r="D394" s="3"/>
+      <c r="D394" s="9" t="s">
+        <v>1223</v>
+      </c>
       <c r="E394" s="4" t="s">
         <v>1163</v>
       </c>
@@ -15944,7 +16020,9 @@
       <c r="C395" s="4" t="s">
         <v>1181</v>
       </c>
-      <c r="D395" s="3"/>
+      <c r="D395" s="9" t="s">
+        <v>1224</v>
+      </c>
       <c r="E395" s="4" t="s">
         <v>1164</v>
       </c>
@@ -15965,7 +16043,9 @@
       <c r="C396" s="4" t="s">
         <v>1182</v>
       </c>
-      <c r="D396" s="3"/>
+      <c r="D396" s="9" t="s">
+        <v>1225</v>
+      </c>
       <c r="E396" s="4" t="s">
         <v>1165</v>
       </c>
@@ -15986,7 +16066,9 @@
       <c r="C397" s="4" t="s">
         <v>1183</v>
       </c>
-      <c r="D397" s="3"/>
+      <c r="D397" s="9" t="s">
+        <v>1226</v>
+      </c>
       <c r="E397" s="4" t="s">
         <v>1166</v>
       </c>
@@ -16007,7 +16089,9 @@
       <c r="C398" s="4" t="s">
         <v>1184</v>
       </c>
-      <c r="D398" s="3"/>
+      <c r="D398" s="9" t="s">
+        <v>1227</v>
+      </c>
       <c r="E398" s="4" t="s">
         <v>1167</v>
       </c>
@@ -16028,7 +16112,9 @@
       <c r="C399" s="4" t="s">
         <v>1185</v>
       </c>
-      <c r="D399" s="3"/>
+      <c r="D399" s="9" t="s">
+        <v>1228</v>
+      </c>
       <c r="E399" s="4" t="s">
         <v>1168</v>
       </c>
@@ -16049,7 +16135,9 @@
       <c r="C400" s="4" t="s">
         <v>1186</v>
       </c>
-      <c r="D400" s="3"/>
+      <c r="D400" s="9" t="s">
+        <v>1229</v>
+      </c>
       <c r="E400" s="4" t="s">
         <v>1169</v>
       </c>
@@ -16101,10 +16189,10 @@
         <v>1191</v>
       </c>
       <c r="F402" s="7">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G402" s="7">
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403" spans="1:7">
@@ -16282,6 +16370,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G410" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}"/>
   <conditionalFormatting sqref="C1:C152 C154:C358">
     <cfRule type="duplicateValues" dxfId="195" priority="267"/>
   </conditionalFormatting>
@@ -16293,24 +16382,24 @@
     <cfRule type="duplicateValues" dxfId="192" priority="251"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C291">
-    <cfRule type="duplicateValues" dxfId="191" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="246" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="247" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="246" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="247" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="242"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C330:C333">
     <cfRule type="duplicateValues" dxfId="183" priority="239"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E21">
-    <cfRule type="duplicateValues" dxfId="182" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="164" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="163" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="180" priority="162" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="163" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="164" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E30">
     <cfRule type="duplicateValues" dxfId="177" priority="165"/>
@@ -16324,136 +16413,136 @@
     <cfRule type="duplicateValues" dxfId="171" priority="187" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31:E61 E22:E29 E7:E20">
-    <cfRule type="duplicateValues" dxfId="170" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="189" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="189" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="188"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37:E56">
     <cfRule type="duplicateValues" dxfId="168" priority="185" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E111">
-    <cfRule type="duplicateValues" dxfId="167" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="154" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="153" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="165" priority="152" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="153" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="154" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="151"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E112:E114 E89:E110 E62:E64">
-    <cfRule type="duplicateValues" dxfId="162" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="259" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="259" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="258"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E112:E114">
-    <cfRule type="duplicateValues" dxfId="160" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="265" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="265" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="264"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E115:E140">
-    <cfRule type="duplicateValues" dxfId="158" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="134" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="135" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="136" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="136" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="135" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="134" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E155:E165">
-    <cfRule type="duplicateValues" dxfId="153" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="121" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="120" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="151" priority="119" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="120" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="121" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="117"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E166:E170 E172:E173">
-    <cfRule type="duplicateValues" dxfId="148" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="114" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="115" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="116" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="115" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="116" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="114" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E171">
-    <cfRule type="duplicateValues" dxfId="143" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="172" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="173" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="174" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="174" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="172" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="173" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E174:E181">
-    <cfRule type="duplicateValues" dxfId="138" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="109" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="110" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="111" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="109" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="111" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="110" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E182">
-    <cfRule type="duplicateValues" dxfId="133" priority="104" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="105" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="104" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="105" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E183:E188">
-    <cfRule type="duplicateValues" dxfId="130" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="157" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="157" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="159" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="127" priority="158" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="159" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="155"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E206:E219">
-    <cfRule type="duplicateValues" dxfId="125" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="103" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="99"/>
     <cfRule type="duplicateValues" dxfId="123" priority="101" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="122" priority="102" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="103" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="100"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E220:E221">
-    <cfRule type="duplicateValues" dxfId="120" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="255" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="118" priority="254" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="255" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="252"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E222:E227">
     <cfRule type="duplicateValues" dxfId="115" priority="257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E235:E239">
-    <cfRule type="duplicateValues" dxfId="114" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="91" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="93" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="111" priority="92" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="93" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="91" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E243:E246">
     <cfRule type="duplicateValues" dxfId="109" priority="84"/>
     <cfRule type="duplicateValues" dxfId="108" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="86" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="87" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="88" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="88" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="86" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="87" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E247:E252">
-    <cfRule type="duplicateValues" dxfId="104" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="81" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="82" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="83" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="81" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="83" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="82" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E254">
-    <cfRule type="duplicateValues" dxfId="99" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="184" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="183" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="97" priority="182" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="183" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="184" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E255:E260">
-    <cfRule type="duplicateValues" dxfId="94" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="71" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="72" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="73" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="73" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="71" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="72" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E261:E266">
-    <cfRule type="duplicateValues" dxfId="89" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="66" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="88" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="66" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="64"/>
     <cfRule type="duplicateValues" dxfId="86" priority="67" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="85" priority="68" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E267:E281">
-    <cfRule type="duplicateValues" dxfId="84" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="59"/>
     <cfRule type="duplicateValues" dxfId="82" priority="61" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="81" priority="62" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="80" priority="63" stopIfTrue="1"/>
@@ -16461,21 +16550,21 @@
   <conditionalFormatting sqref="E282:E291">
     <cfRule type="duplicateValues" dxfId="79" priority="51"/>
     <cfRule type="duplicateValues" dxfId="78" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="57" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="58" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="58" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="57" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E292:E295">
-    <cfRule type="duplicateValues" dxfId="71" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="49" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="49" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="45"/>
     <cfRule type="duplicateValues" dxfId="64" priority="50" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E296:E297">
@@ -16485,20 +16574,20 @@
     <cfRule type="duplicateValues" dxfId="60" priority="213"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E304:E308">
-    <cfRule type="duplicateValues" dxfId="59" priority="214" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="214" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E309:E314">
-    <cfRule type="duplicateValues" dxfId="55" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="224" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="225" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="225" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="224" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="218"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E315:E326">
     <cfRule type="duplicateValues" dxfId="47" priority="231"/>
@@ -16507,58 +16596,58 @@
     <cfRule type="duplicateValues" dxfId="44" priority="234"/>
     <cfRule type="duplicateValues" dxfId="43" priority="235"/>
     <cfRule type="duplicateValues" dxfId="42" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="237" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="238" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="238" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="237" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E327">
-    <cfRule type="duplicateValues" dxfId="39" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="41" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="42" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="42" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="41" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E328">
-    <cfRule type="duplicateValues" dxfId="31" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="33" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
     <cfRule type="duplicateValues" dxfId="24" priority="34" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E329">
-    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="25" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="26" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="25" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E331:E357">
     <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="10" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="9" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
     <cfRule type="duplicateValues" dxfId="11" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E359:E410">
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="18" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
     <cfRule type="duplicateValues" dxfId="1" priority="17" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="18" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Cambium_Import_Details.xlsx
+++ b/Cambium_Import_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\czad\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A4C236-A017-4ECE-8892-53621287C56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601AE856-24C0-4AC6-8E7B-B084A9CCF1A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{42E993CD-9B70-4509-B668-6EEF51FEBD70}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$410</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$412</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="1240">
   <si>
     <t>SR NO</t>
   </si>
@@ -3698,6 +3698,9 @@
     <t>B0GN86G345</t>
   </si>
   <si>
+    <t>Remarks</t>
+  </si>
+  <si>
     <t>B0GW8Z556N</t>
   </si>
   <si>
@@ -3747,6 +3750,33 @@
   </si>
   <si>
     <t>B0GTZ9X8Q2</t>
+  </si>
+  <si>
+    <t>FBA80109</t>
+  </si>
+  <si>
+    <t>FBA80110</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>X5</t>
+  </si>
+  <si>
+    <t>B0GXPBHDRF</t>
+  </si>
+  <si>
+    <t>B0GXP97CZG</t>
+  </si>
+  <si>
+    <t>B0GXP7LJ75</t>
+  </si>
+  <si>
+    <t>B0GN94YDY2</t>
+  </si>
+  <si>
+    <t>B0GN8WW6BC</t>
   </si>
 </sst>
 </file>
@@ -3808,7 +3838,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3827,8 +3857,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3851,12 +3887,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3878,7 +3925,11 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6936,7 +6987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}">
-  <dimension ref="A1:G410"/>
+  <dimension ref="A1:H412"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -6948,7 +6999,7 @@
     <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -6970,8 +7021,11 @@
       <c r="G1" s="5" t="s">
         <v>1139</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="9" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -6994,7 +7048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -7017,7 +7071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -7040,7 +7094,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -7063,7 +7117,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -7086,7 +7140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -7109,7 +7163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -7132,7 +7186,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -7155,7 +7209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -7178,7 +7232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:8">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -7201,7 +7255,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -7224,7 +7278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:8">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -7247,7 +7301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -7270,7 +7324,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:8">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -7293,7 +7347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -9547,7 +9601,7 @@
         <v>0</v>
       </c>
       <c r="G113" s="7">
-        <v>0</v>
+        <v>504</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -9895,7 +9949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:8">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -9918,7 +9972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:8">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -9941,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="16.8">
+    <row r="131" spans="1:8" ht="16.8">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -9964,7 +10018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:8">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -9987,7 +10041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:8">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -10010,7 +10064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:8">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -10033,7 +10087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:8">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -10056,7 +10110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:8">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -10079,7 +10133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:8">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -10101,8 +10155,9 @@
       <c r="G137" s="8">
         <v>1472</v>
       </c>
-    </row>
-    <row r="138" spans="1:7">
+      <c r="H137" s="10"/>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -10125,7 +10180,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:8">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -10148,7 +10203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:8">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -10171,7 +10226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:8">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -10194,7 +10249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:8">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -10217,7 +10272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:8">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -10240,7 +10295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:8">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -10421,7 +10476,7 @@
         <v>0</v>
       </c>
       <c r="G151" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -11249,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="G187" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -15767,8 +15822,8 @@
       <c r="C384" s="4" t="s">
         <v>1170</v>
       </c>
-      <c r="D384" s="9" t="s">
-        <v>1213</v>
+      <c r="D384" s="11" t="s">
+        <v>1214</v>
       </c>
       <c r="E384" s="4" t="s">
         <v>1153</v>
@@ -15790,8 +15845,8 @@
       <c r="C385" s="4" t="s">
         <v>1171</v>
       </c>
-      <c r="D385" s="9" t="s">
-        <v>1214</v>
+      <c r="D385" s="11" t="s">
+        <v>1215</v>
       </c>
       <c r="E385" s="4" t="s">
         <v>1154</v>
@@ -15813,8 +15868,8 @@
       <c r="C386" s="4" t="s">
         <v>1172</v>
       </c>
-      <c r="D386" s="9" t="s">
-        <v>1215</v>
+      <c r="D386" s="11" t="s">
+        <v>1216</v>
       </c>
       <c r="E386" s="4" t="s">
         <v>1155</v>
@@ -15836,8 +15891,8 @@
       <c r="C387" s="4" t="s">
         <v>1173</v>
       </c>
-      <c r="D387" s="9" t="s">
-        <v>1216</v>
+      <c r="D387" s="11" t="s">
+        <v>1217</v>
       </c>
       <c r="E387" s="4" t="s">
         <v>1156</v>
@@ -15859,8 +15914,8 @@
       <c r="C388" s="4" t="s">
         <v>1174</v>
       </c>
-      <c r="D388" s="9" t="s">
-        <v>1217</v>
+      <c r="D388" s="11" t="s">
+        <v>1218</v>
       </c>
       <c r="E388" s="4" t="s">
         <v>1157</v>
@@ -15882,8 +15937,8 @@
       <c r="C389" s="4" t="s">
         <v>1175</v>
       </c>
-      <c r="D389" s="9" t="s">
-        <v>1218</v>
+      <c r="D389" s="11" t="s">
+        <v>1219</v>
       </c>
       <c r="E389" s="4" t="s">
         <v>1158</v>
@@ -15905,8 +15960,8 @@
       <c r="C390" s="4" t="s">
         <v>1176</v>
       </c>
-      <c r="D390" s="9" t="s">
-        <v>1219</v>
+      <c r="D390" s="11" t="s">
+        <v>1220</v>
       </c>
       <c r="E390" s="4" t="s">
         <v>1159</v>
@@ -15928,8 +15983,8 @@
       <c r="C391" s="4" t="s">
         <v>1177</v>
       </c>
-      <c r="D391" s="9" t="s">
-        <v>1220</v>
+      <c r="D391" s="11" t="s">
+        <v>1221</v>
       </c>
       <c r="E391" s="4" t="s">
         <v>1160</v>
@@ -15951,8 +16006,8 @@
       <c r="C392" s="4" t="s">
         <v>1178</v>
       </c>
-      <c r="D392" s="9" t="s">
-        <v>1221</v>
+      <c r="D392" s="11" t="s">
+        <v>1222</v>
       </c>
       <c r="E392" s="4" t="s">
         <v>1161</v>
@@ -15974,8 +16029,8 @@
       <c r="C393" s="4" t="s">
         <v>1179</v>
       </c>
-      <c r="D393" s="9" t="s">
-        <v>1222</v>
+      <c r="D393" s="11" t="s">
+        <v>1223</v>
       </c>
       <c r="E393" s="4" t="s">
         <v>1162</v>
@@ -15997,8 +16052,8 @@
       <c r="C394" s="4" t="s">
         <v>1180</v>
       </c>
-      <c r="D394" s="9" t="s">
-        <v>1223</v>
+      <c r="D394" s="11" t="s">
+        <v>1224</v>
       </c>
       <c r="E394" s="4" t="s">
         <v>1163</v>
@@ -16020,8 +16075,8 @@
       <c r="C395" s="4" t="s">
         <v>1181</v>
       </c>
-      <c r="D395" s="9" t="s">
-        <v>1224</v>
+      <c r="D395" s="11" t="s">
+        <v>1225</v>
       </c>
       <c r="E395" s="4" t="s">
         <v>1164</v>
@@ -16043,8 +16098,8 @@
       <c r="C396" s="4" t="s">
         <v>1182</v>
       </c>
-      <c r="D396" s="9" t="s">
-        <v>1225</v>
+      <c r="D396" s="11" t="s">
+        <v>1226</v>
       </c>
       <c r="E396" s="4" t="s">
         <v>1165</v>
@@ -16066,8 +16121,8 @@
       <c r="C397" s="4" t="s">
         <v>1183</v>
       </c>
-      <c r="D397" s="9" t="s">
-        <v>1226</v>
+      <c r="D397" s="11" t="s">
+        <v>1227</v>
       </c>
       <c r="E397" s="4" t="s">
         <v>1166</v>
@@ -16089,8 +16144,8 @@
       <c r="C398" s="4" t="s">
         <v>1184</v>
       </c>
-      <c r="D398" s="9" t="s">
-        <v>1227</v>
+      <c r="D398" s="11" t="s">
+        <v>1228</v>
       </c>
       <c r="E398" s="4" t="s">
         <v>1167</v>
@@ -16112,8 +16167,8 @@
       <c r="C399" s="4" t="s">
         <v>1185</v>
       </c>
-      <c r="D399" s="9" t="s">
-        <v>1228</v>
+      <c r="D399" s="11" t="s">
+        <v>1229</v>
       </c>
       <c r="E399" s="4" t="s">
         <v>1168</v>
@@ -16135,8 +16190,8 @@
       <c r="C400" s="4" t="s">
         <v>1186</v>
       </c>
-      <c r="D400" s="9" t="s">
-        <v>1229</v>
+      <c r="D400" s="11" t="s">
+        <v>1230</v>
       </c>
       <c r="E400" s="4" t="s">
         <v>1169</v>
@@ -16274,7 +16329,9 @@
       <c r="C406" s="4" t="s">
         <v>1205</v>
       </c>
-      <c r="D406" s="3"/>
+      <c r="D406" s="3" t="s">
+        <v>1238</v>
+      </c>
       <c r="E406" s="4" t="s">
         <v>1195</v>
       </c>
@@ -16295,7 +16352,9 @@
       <c r="C407" s="4" t="s">
         <v>1206</v>
       </c>
-      <c r="D407" s="3"/>
+      <c r="D407" s="3" t="s">
+        <v>1239</v>
+      </c>
       <c r="E407" s="4" t="s">
         <v>1196</v>
       </c>
@@ -16316,7 +16375,9 @@
       <c r="C408" s="4" t="s">
         <v>1199</v>
       </c>
-      <c r="D408" s="3"/>
+      <c r="D408" s="3" t="s">
+        <v>1235</v>
+      </c>
       <c r="E408" s="4" t="s">
         <v>1197</v>
       </c>
@@ -16337,7 +16398,9 @@
       <c r="C409" s="4" t="s">
         <v>1200</v>
       </c>
-      <c r="D409" s="3"/>
+      <c r="D409" s="3" t="s">
+        <v>1236</v>
+      </c>
       <c r="E409" s="4" t="s">
         <v>1198</v>
       </c>
@@ -16358,7 +16421,9 @@
       <c r="C410" s="4" t="s">
         <v>1208</v>
       </c>
-      <c r="D410" s="3"/>
+      <c r="D410" s="3" t="s">
+        <v>1237</v>
+      </c>
       <c r="E410" s="4" t="s">
         <v>1207</v>
       </c>
@@ -16369,8 +16434,49 @@
         <v>0</v>
       </c>
     </row>
+    <row r="411" spans="1:7">
+      <c r="A411" s="1">
+        <v>410</v>
+      </c>
+      <c r="B411" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C411" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D411" s="3"/>
+      <c r="E411" s="4" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F411" s="7">
+        <v>0</v>
+      </c>
+      <c r="G411" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7">
+      <c r="A412" s="1">
+        <v>411</v>
+      </c>
+      <c r="B412" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C412" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D412" s="3"/>
+      <c r="E412" s="4" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F412" s="7">
+        <v>0</v>
+      </c>
+      <c r="G412" s="7">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G410" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}"/>
   <conditionalFormatting sqref="C1:C152 C154:C358">
     <cfRule type="duplicateValues" dxfId="195" priority="267"/>
   </conditionalFormatting>
@@ -16639,7 +16745,7 @@
     <cfRule type="duplicateValues" dxfId="9" priority="5"/>
     <cfRule type="duplicateValues" dxfId="8" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E359:E410">
+  <conditionalFormatting sqref="E359:E412">
     <cfRule type="duplicateValues" dxfId="7" priority="16"/>
     <cfRule type="duplicateValues" dxfId="6" priority="15"/>
     <cfRule type="duplicateValues" dxfId="5" priority="14"/>

--- a/Cambium_Import_Details.xlsx
+++ b/Cambium_Import_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rusha\Downloads\Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08918BF-1489-4CBD-893D-D17262CD6B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B54589E-3543-445E-96C6-CA0B4FAED09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42E993CD-9B70-4509-B668-6EEF51FEBD70}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$431</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$493</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1706" uniqueCount="1280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1949" uniqueCount="1449">
   <si>
     <t>SR NO</t>
   </si>
@@ -3317,9 +3317,6 @@
     <t>B0G53LZNY3</t>
   </si>
   <si>
-    <t>AM-Mix8</t>
-  </si>
-  <si>
     <t>FBA79963</t>
   </si>
   <si>
@@ -3608,9 +3605,6 @@
     <t>FBA80014</t>
   </si>
   <si>
-    <t>AM-Mix4 OTG</t>
-  </si>
-  <si>
     <t>AM-S2</t>
   </si>
   <si>
@@ -3888,6 +3882,519 @@
   </si>
   <si>
     <t>AA-27</t>
+  </si>
+  <si>
+    <t>FBA80142</t>
+  </si>
+  <si>
+    <t>AM-C5 White</t>
+  </si>
+  <si>
+    <t>AH-53</t>
+  </si>
+  <si>
+    <t>AH-50-DH</t>
+  </si>
+  <si>
+    <t>AH-40 Pro</t>
+  </si>
+  <si>
+    <t>AH-53 Pro</t>
+  </si>
+  <si>
+    <t>FBA80114</t>
+  </si>
+  <si>
+    <t>FBA80115</t>
+  </si>
+  <si>
+    <t>FBA80116</t>
+  </si>
+  <si>
+    <t>FBA80117</t>
+  </si>
+  <si>
+    <t>FBA80074</t>
+  </si>
+  <si>
+    <t>FBA80075</t>
+  </si>
+  <si>
+    <t>FBA80076</t>
+  </si>
+  <si>
+    <t>FBA80077</t>
+  </si>
+  <si>
+    <t>FBA80104</t>
+  </si>
+  <si>
+    <t>FBA80105</t>
+  </si>
+  <si>
+    <t>FBA80106</t>
+  </si>
+  <si>
+    <t>PB-15 (AH-50+AM-C2+AI-04)</t>
+  </si>
+  <si>
+    <t>PB-16 (AH-50+AI-13+AM-C2)</t>
+  </si>
+  <si>
+    <t>PB-17 (AH-40-SL+AM-C43+AI-13)</t>
+  </si>
+  <si>
+    <t>PB-18 (AH-45-BK+AI-03+AM-C39)</t>
+  </si>
+  <si>
+    <t>UB-04 (AM-S2+AA-21+AI-04+AM-C2)</t>
+  </si>
+  <si>
+    <t>UB-05 (AM-S2+AA-21)</t>
+  </si>
+  <si>
+    <t>UB-06 (AM-S2+AA-22)</t>
+  </si>
+  <si>
+    <t>B0H1H3K6B2</t>
+  </si>
+  <si>
+    <t>FBA80128</t>
+  </si>
+  <si>
+    <t>B0H1MTP2ZP</t>
+  </si>
+  <si>
+    <t>FBA80143</t>
+  </si>
+  <si>
+    <t>FBA80141</t>
+  </si>
+  <si>
+    <t>B0FJS57732</t>
+  </si>
+  <si>
+    <t>B0GD8JSPB1</t>
+  </si>
+  <si>
+    <t>FBA79974</t>
+  </si>
+  <si>
+    <t>B0G2C2RCXN</t>
+  </si>
+  <si>
+    <t>B0GKPXQ8G3</t>
+  </si>
+  <si>
+    <t>FBA79967</t>
+  </si>
+  <si>
+    <t>FBA80016</t>
+  </si>
+  <si>
+    <t>B0FLYHJ6DK</t>
+  </si>
+  <si>
+    <t>B0FLYJFC22</t>
+  </si>
+  <si>
+    <t>FBK79009</t>
+  </si>
+  <si>
+    <t>FBK79010</t>
+  </si>
+  <si>
+    <t>B0GY827J9C</t>
+  </si>
+  <si>
+    <t>B0GXPGBQB1</t>
+  </si>
+  <si>
+    <t>B0GY857139</t>
+  </si>
+  <si>
+    <t>B0GY86ZT1X</t>
+  </si>
+  <si>
+    <t>B0GXY7YJWP</t>
+  </si>
+  <si>
+    <t>B0H2FNV2RC</t>
+  </si>
+  <si>
+    <t>B0H2FCK54H</t>
+  </si>
+  <si>
+    <t>FBA79821</t>
+  </si>
+  <si>
+    <t>B0FJ2JJZL3</t>
+  </si>
+  <si>
+    <t>FBA79904</t>
+  </si>
+  <si>
+    <t>B0FTVQQVDC</t>
+  </si>
+  <si>
+    <t>FBA79827</t>
+  </si>
+  <si>
+    <t>B0FJ8S5XJ8</t>
+  </si>
+  <si>
+    <t>FBA79906</t>
+  </si>
+  <si>
+    <t>B0FTVVLNS9</t>
+  </si>
+  <si>
+    <t>FBA79969</t>
+  </si>
+  <si>
+    <t>B0G3B677Z5</t>
+  </si>
+  <si>
+    <t>FBA79845</t>
+  </si>
+  <si>
+    <t>B0FN7B3KWS</t>
+  </si>
+  <si>
+    <t>FBA79823</t>
+  </si>
+  <si>
+    <t>B0FJ2HZCVN</t>
+  </si>
+  <si>
+    <t>FBA79655</t>
+  </si>
+  <si>
+    <t>B0DN6PFWNK</t>
+  </si>
+  <si>
+    <t>FBA79824</t>
+  </si>
+  <si>
+    <t>B0FJ2K95XT</t>
+  </si>
+  <si>
+    <t>FBA79833</t>
+  </si>
+  <si>
+    <t>B0FJ8PZ9H7</t>
+  </si>
+  <si>
+    <t>FBA79826</t>
+  </si>
+  <si>
+    <t>B0FJ2LQT7K</t>
+  </si>
+  <si>
+    <t>FBA79903</t>
+  </si>
+  <si>
+    <t>B0FR5DLXH9</t>
+  </si>
+  <si>
+    <t>FBA79653</t>
+  </si>
+  <si>
+    <t>B0DN6LJZBR</t>
+  </si>
+  <si>
+    <t>FBK79708</t>
+  </si>
+  <si>
+    <t>B0FJS7JZ4V</t>
+  </si>
+  <si>
+    <t>FBA79825</t>
+  </si>
+  <si>
+    <t>B0FJ2DT13L</t>
+  </si>
+  <si>
+    <t>FBA79844</t>
+  </si>
+  <si>
+    <t>B0FN7DYB2M</t>
+  </si>
+  <si>
+    <t>FBA79830</t>
+  </si>
+  <si>
+    <t>B0FJ8TSQK1</t>
+  </si>
+  <si>
+    <t>FBA79846</t>
+  </si>
+  <si>
+    <t>B0FN7C25VS</t>
+  </si>
+  <si>
+    <t>FBA79832</t>
+  </si>
+  <si>
+    <t>B0FJ8S53GW</t>
+  </si>
+  <si>
+    <t>FBA79822</t>
+  </si>
+  <si>
+    <t>B0FJ2J6MTF</t>
+  </si>
+  <si>
+    <t>FBA79909</t>
+  </si>
+  <si>
+    <t>B0FVM17Q4W</t>
+  </si>
+  <si>
+    <t>FBAM75673</t>
+  </si>
+  <si>
+    <t>B0DFTVZPM8</t>
+  </si>
+  <si>
+    <t>FBA79814</t>
+  </si>
+  <si>
+    <t>B0GNM35G8X</t>
+  </si>
+  <si>
+    <t>FBA79465</t>
+  </si>
+  <si>
+    <t>B0DFMQCGT1</t>
+  </si>
+  <si>
+    <t>FBA79835</t>
+  </si>
+  <si>
+    <t>B0FJ8TWCQZ</t>
+  </si>
+  <si>
+    <t>FBA79834</t>
+  </si>
+  <si>
+    <t>B0FJ8T4WXM</t>
+  </si>
+  <si>
+    <t>FBA79905</t>
+  </si>
+  <si>
+    <t>B0FTVSH458</t>
+  </si>
+  <si>
+    <t>FBA79907</t>
+  </si>
+  <si>
+    <t>B0FTVS34SD</t>
+  </si>
+  <si>
+    <t>FBA79908</t>
+  </si>
+  <si>
+    <t>B0FTVV1QJY</t>
+  </si>
+  <si>
+    <t>FBA79831</t>
+  </si>
+  <si>
+    <t>B0FJ8W5Y9Q</t>
+  </si>
+  <si>
+    <t>FBA79012</t>
+  </si>
+  <si>
+    <t>B0CH4THGGM</t>
+  </si>
+  <si>
+    <t>FBA78970</t>
+  </si>
+  <si>
+    <t>B0CF5T1LFR</t>
+  </si>
+  <si>
+    <t>FBA78977</t>
+  </si>
+  <si>
+    <t>B0CF5TVDRT</t>
+  </si>
+  <si>
+    <t>FBA78978</t>
+  </si>
+  <si>
+    <t>B0CF5PCL34</t>
+  </si>
+  <si>
+    <t>FBA79389</t>
+  </si>
+  <si>
+    <t>B0D3M13T6H</t>
+  </si>
+  <si>
+    <t>FBA79180</t>
+  </si>
+  <si>
+    <t>B0CPXVV5XN</t>
+  </si>
+  <si>
+    <t>FBA79181</t>
+  </si>
+  <si>
+    <t>B0CPXXJM6C</t>
+  </si>
+  <si>
+    <t>FBA79182</t>
+  </si>
+  <si>
+    <t>B0CPXXYY6H</t>
+  </si>
+  <si>
+    <t>FBA79183</t>
+  </si>
+  <si>
+    <t>B0CPXWXCBS</t>
+  </si>
+  <si>
+    <t>FBA79836</t>
+  </si>
+  <si>
+    <t>B0FJ8Z1W81</t>
+  </si>
+  <si>
+    <t>FBA79837</t>
+  </si>
+  <si>
+    <t>B0FJ8V2LZM</t>
+  </si>
+  <si>
+    <t>FBA79847</t>
+  </si>
+  <si>
+    <t>B0FN7FYZM3</t>
+  </si>
+  <si>
+    <t>UB-01 (AI-04, AM-S1, AA-21, AM-C2)</t>
+  </si>
+  <si>
+    <t>PB-10 (AM-C2+AI-04+AH-60-BL)</t>
+  </si>
+  <si>
+    <t>PB-03 (AI-04 Red + AM-C11 x 2)</t>
+  </si>
+  <si>
+    <t>PB-12 (AM-C11+AA-05+AI-04+AH-60-RD)</t>
+  </si>
+  <si>
+    <t>UB-03 (AM-S1 + AA-22)</t>
+  </si>
+  <si>
+    <t>UB-02 (AM-S1 + AA-21)</t>
+  </si>
+  <si>
+    <t>PB-01 (AM-C11 + AI-04)</t>
+  </si>
+  <si>
+    <t>AM-C44 Pro</t>
+  </si>
+  <si>
+    <t>GB-01 (AM-C43 +AI-10)</t>
+  </si>
+  <si>
+    <t>PB-04 (AI-04 Red + AM-C44 x 2)</t>
+  </si>
+  <si>
+    <t>PB-02 (AI-04 Red + AM-C11 + AA-05)</t>
+  </si>
+  <si>
+    <t>AA-25M</t>
+  </si>
+  <si>
+    <t>AM-C45 Pro</t>
+  </si>
+  <si>
+    <t>GB-02 (AM-C43 + AI-11)</t>
+  </si>
+  <si>
+    <t>PB-08 (AM-C1 + AI-04)</t>
+  </si>
+  <si>
+    <t>GB-03 (AI-12 + AM-C43)</t>
+  </si>
+  <si>
+    <t>AM-C11X Pro</t>
+  </si>
+  <si>
+    <t>GB-05 (AM-C43 + AI-06)</t>
+  </si>
+  <si>
+    <t>KB-01 (AM-W32 + AI-12)</t>
+  </si>
+  <si>
+    <t>AH-50 Ear Cushion</t>
+  </si>
+  <si>
+    <t>PB-06 (AA-05 + AM-C44 + AI-04)</t>
+  </si>
+  <si>
+    <t>PB-05 (AA-05 + AM-C11 + AI-04)</t>
+  </si>
+  <si>
+    <t>PB-11 (AM-C44+AA-05+AH-45-BK)</t>
+  </si>
+  <si>
+    <t>PB-13 (AM-C43+AH-40-SL+AI-11)</t>
+  </si>
+  <si>
+    <t>PB-14 (AM-C43+AH-40-SL+AI-12)</t>
+  </si>
+  <si>
+    <t>GB-04 (AM-C45 + AI-06)</t>
+  </si>
+  <si>
+    <t>AI-07</t>
+  </si>
+  <si>
+    <t>AA-16</t>
+  </si>
+  <si>
+    <t>AA-23</t>
+  </si>
+  <si>
+    <t>AA-24</t>
+  </si>
+  <si>
+    <t>AWB-01</t>
+  </si>
+  <si>
+    <t>AB-02 (AI-04 Red + AM-C2)</t>
+  </si>
+  <si>
+    <t>AB-03 (AM-C11+ AI-04 + AA-05)</t>
+  </si>
+  <si>
+    <t>AB-04 (2xAM-C2 + AI-04 Red)</t>
+  </si>
+  <si>
+    <t>AB-05 (2xAM-C11+AI-04Red+2xAA-05)</t>
+  </si>
+  <si>
+    <t>PB-07 (AA-05 + AM-C45 + AI-04)</t>
+  </si>
+  <si>
+    <t>AI-06 + AM-C45</t>
+  </si>
+  <si>
+    <t>PB-09 (AM-C45 + AI-06 + AA-05)</t>
+  </si>
+  <si>
+    <t>AM-Pro8</t>
+  </si>
+  <si>
+    <t>BE-4T</t>
   </si>
 </sst>
 </file>
@@ -3957,7 +4464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3973,6 +4480,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4012,11 +4525,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4043,13 +4557,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 6" xfId="2" xr:uid="{6868F595-51BB-48AA-B4D1-2993B8A000FF}"/>
   </cellStyles>
   <dxfs count="196">
     <dxf>
@@ -7101,26 +7619,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}">
-  <dimension ref="A1:I431"/>
+  <dimension ref="A1:I493"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="F1" s="9">
-        <f>SUBTOTAL(9,F3:F431)</f>
-        <v>12152</v>
+        <f>SUBTOTAL(9,F3:F493)</f>
+        <v>26128</v>
       </c>
       <c r="G1" s="9">
-        <f>SUBTOTAL(9,G3:G431)</f>
-        <v>36607</v>
+        <f>SUBTOTAL(9,G3:G493)</f>
+        <v>23639</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7140,13 +7658,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>1138</v>
-      </c>
       <c r="H2" s="10" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -7212,10 +7730,10 @@
         <v>12</v>
       </c>
       <c r="F5" s="7">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="G5" s="7">
-        <v>1008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -7235,10 +7753,10 @@
         <v>15</v>
       </c>
       <c r="F6" s="7">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G6" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -7442,10 +7960,10 @@
         <v>42</v>
       </c>
       <c r="F15" s="7">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G15" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -7626,10 +8144,10 @@
         <v>66</v>
       </c>
       <c r="F23" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G23" s="7">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7718,10 +8236,10 @@
         <v>78</v>
       </c>
       <c r="F27" s="7">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="G27" s="7">
-        <v>504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -7833,10 +8351,10 @@
         <v>93</v>
       </c>
       <c r="F32" s="7">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="G32" s="7">
-        <v>504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7994,10 +8512,10 @@
         <v>114</v>
       </c>
       <c r="F39" s="7">
-        <v>0</v>
+        <v>512</v>
       </c>
       <c r="G39" s="7">
-        <v>512</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -8248,10 +8766,10 @@
         <v>147</v>
       </c>
       <c r="F50" s="7">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="G50" s="7">
-        <v>504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -9216,7 +9734,7 @@
         <v>274</v>
       </c>
       <c r="F92" s="7">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G92" s="7">
         <v>0</v>
@@ -10925,10 +11443,10 @@
         <v>0</v>
       </c>
       <c r="H166" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="I166" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -12328,10 +12846,10 @@
         <v>682</v>
       </c>
       <c r="F227" s="7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G227" s="8">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -14697,10 +15215,10 @@
         <v>991</v>
       </c>
       <c r="F330" s="7">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="G330" s="7">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -14720,10 +15238,10 @@
         <v>994</v>
       </c>
       <c r="F331" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="G331" s="7">
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:7">
@@ -15430,7 +15948,7 @@
         <v>1088</v>
       </c>
       <c r="E362" s="4" t="s">
-        <v>1186</v>
+        <v>1448</v>
       </c>
       <c r="F362" s="7">
         <v>0</v>
@@ -15447,13 +15965,13 @@
         <v>8</v>
       </c>
       <c r="C363" s="4" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D363" s="3" t="s">
         <v>1090</v>
       </c>
-      <c r="D363" s="3" t="s">
-        <v>1091</v>
-      </c>
       <c r="E363" s="4" t="s">
-        <v>1089</v>
+        <v>1447</v>
       </c>
       <c r="F363" s="7">
         <v>0</v>
@@ -15470,13 +15988,13 @@
         <v>8</v>
       </c>
       <c r="C364" s="4" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D364" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="D364" s="3" t="s">
-        <v>1094</v>
-      </c>
       <c r="E364" s="4" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F364" s="7">
         <v>0</v>
@@ -15493,13 +16011,13 @@
         <v>8</v>
       </c>
       <c r="C365" s="4" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D365" s="3" t="s">
         <v>1096</v>
       </c>
-      <c r="D365" s="3" t="s">
-        <v>1097</v>
-      </c>
       <c r="E365" s="4" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="F365" s="7">
         <v>0</v>
@@ -15516,13 +16034,13 @@
         <v>8</v>
       </c>
       <c r="C366" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D366" s="3" t="s">
         <v>1099</v>
       </c>
-      <c r="D366" s="3" t="s">
-        <v>1100</v>
-      </c>
       <c r="E366" s="4" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F366" s="7">
         <v>0</v>
@@ -15539,13 +16057,13 @@
         <v>8</v>
       </c>
       <c r="C367" s="4" t="s">
+        <v>1101</v>
+      </c>
+      <c r="D367" s="3" t="s">
         <v>1102</v>
       </c>
-      <c r="D367" s="3" t="s">
-        <v>1103</v>
-      </c>
       <c r="E367" s="4" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F367" s="7">
         <v>0</v>
@@ -15562,13 +16080,13 @@
         <v>8</v>
       </c>
       <c r="C368" s="4" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D368" s="3" t="s">
         <v>1105</v>
       </c>
-      <c r="D368" s="3" t="s">
-        <v>1106</v>
-      </c>
       <c r="E368" s="4" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F368" s="7">
         <v>200</v>
@@ -15585,13 +16103,13 @@
         <v>8</v>
       </c>
       <c r="C369" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="D369" s="3" t="s">
         <v>1108</v>
       </c>
-      <c r="D369" s="3" t="s">
-        <v>1109</v>
-      </c>
       <c r="E369" s="4" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="F369" s="7">
         <v>0</v>
@@ -15608,13 +16126,13 @@
         <v>8</v>
       </c>
       <c r="C370" s="4" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D370" s="3" t="s">
         <v>1111</v>
       </c>
-      <c r="D370" s="3" t="s">
-        <v>1112</v>
-      </c>
       <c r="E370" s="4" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F370" s="7">
         <v>0</v>
@@ -15631,13 +16149,13 @@
         <v>8</v>
       </c>
       <c r="C371" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="D371" s="3" t="s">
         <v>1114</v>
       </c>
-      <c r="D371" s="3" t="s">
-        <v>1115</v>
-      </c>
       <c r="E371" s="4" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F371" s="7">
         <v>0</v>
@@ -15654,13 +16172,13 @@
         <v>8</v>
       </c>
       <c r="C372" s="4" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D372" s="3" t="s">
         <v>1117</v>
       </c>
-      <c r="D372" s="3" t="s">
-        <v>1118</v>
-      </c>
       <c r="E372" s="4" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="F372" s="7">
         <v>0</v>
@@ -15677,13 +16195,13 @@
         <v>656</v>
       </c>
       <c r="C373" s="4" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D373" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="D373" s="3" t="s">
-        <v>1121</v>
-      </c>
       <c r="E373" s="4" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="F373" s="7">
         <v>0</v>
@@ -15700,13 +16218,13 @@
         <v>8</v>
       </c>
       <c r="C374" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D374" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="D374" s="3" t="s">
-        <v>1124</v>
-      </c>
       <c r="E374" s="4" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="F374" s="7">
         <v>0</v>
@@ -15723,13 +16241,13 @@
         <v>656</v>
       </c>
       <c r="C375" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D375" s="3" t="s">
         <v>1126</v>
       </c>
-      <c r="D375" s="3" t="s">
-        <v>1127</v>
-      </c>
       <c r="E375" s="4" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="F375" s="7">
         <v>0</v>
@@ -15746,13 +16264,13 @@
         <v>8</v>
       </c>
       <c r="C376" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D376" s="3" t="s">
         <v>1129</v>
       </c>
-      <c r="D376" s="3" t="s">
-        <v>1130</v>
-      </c>
       <c r="E376" s="4" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="F376" s="7">
         <v>0</v>
@@ -15769,13 +16287,13 @@
         <v>8</v>
       </c>
       <c r="C377" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D377" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="D377" s="3" t="s">
-        <v>1133</v>
-      </c>
       <c r="E377" s="4" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="F377" s="7">
         <v>0</v>
@@ -15792,13 +16310,13 @@
         <v>8</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="E378" s="4" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="F378" s="7">
         <v>0</v>
@@ -15815,13 +16333,13 @@
         <v>8</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D379" s="3" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="E379" s="4" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="F379" s="7">
         <v>0</v>
@@ -15838,13 +16356,13 @@
         <v>8</v>
       </c>
       <c r="C380" s="4" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D380" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="D380" s="3" t="s">
-        <v>1124</v>
-      </c>
       <c r="E380" s="4" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F380" s="7">
         <v>0</v>
@@ -15861,13 +16379,13 @@
         <v>8</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E381" s="4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F381" s="7">
         <v>0</v>
@@ -15884,13 +16402,13 @@
         <v>8</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="E382" s="4" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="F382" s="7">
         <v>0</v>
@@ -15907,13 +16425,13 @@
         <v>8</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="E383" s="4" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="F383" s="7">
         <v>0</v>
@@ -15930,13 +16448,13 @@
         <v>8</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="E384" s="4" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="F384" s="7">
         <v>0</v>
@@ -15953,13 +16471,13 @@
         <v>8</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="E385" s="4" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="F385" s="7">
         <v>0</v>
@@ -15976,13 +16494,13 @@
         <v>8</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="E386" s="4" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F386" s="7">
         <v>0</v>
@@ -15999,13 +16517,13 @@
         <v>8</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="E387" s="4" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="F387" s="7">
         <v>0</v>
@@ -16022,13 +16540,13 @@
         <v>8</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="E388" s="4" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F388" s="7">
         <v>0</v>
@@ -16045,13 +16563,13 @@
         <v>8</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="E389" s="4" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="F389" s="7">
         <v>0</v>
@@ -16068,13 +16586,13 @@
         <v>8</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="E390" s="4" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="F390" s="7">
         <v>0</v>
@@ -16091,13 +16609,13 @@
         <v>8</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D391" s="3" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="E391" s="4" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="F391" s="7">
         <v>0</v>
@@ -16114,13 +16632,13 @@
         <v>8</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E392" s="4" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F392" s="7">
         <v>0</v>
@@ -16137,13 +16655,13 @@
         <v>8</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D393" s="3" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="E393" s="4" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="F393" s="7">
         <v>0</v>
@@ -16160,13 +16678,13 @@
         <v>8</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="E394" s="4" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="F394" s="7">
         <v>0</v>
@@ -16183,13 +16701,13 @@
         <v>8</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="E395" s="4" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="F395" s="7">
         <v>0</v>
@@ -16206,13 +16724,13 @@
         <v>8</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E396" s="4" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="F396" s="7">
         <v>0</v>
@@ -16229,13 +16747,13 @@
         <v>8</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E397" s="4" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F397" s="7">
         <v>0</v>
@@ -16252,13 +16770,13 @@
         <v>8</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="E398" s="4" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="F398" s="7">
         <v>0</v>
@@ -16275,13 +16793,13 @@
         <v>8</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="E399" s="4" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="F399" s="7">
         <v>0</v>
@@ -16298,13 +16816,13 @@
         <v>8</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="E400" s="4" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F400" s="7">
         <v>0</v>
@@ -16321,13 +16839,13 @@
         <v>8</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="F401" s="7">
         <v>0</v>
@@ -16344,13 +16862,13 @@
         <v>8</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E402" s="4" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="F402" s="7">
         <v>0</v>
@@ -16367,13 +16885,13 @@
         <v>656</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="E403" s="4" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="F403" s="7">
         <v>0</v>
@@ -16390,13 +16908,13 @@
         <v>656</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="E404" s="4" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="F404" s="7">
         <v>504</v>
@@ -16413,13 +16931,13 @@
         <v>656</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="E405" s="4" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="F405" s="7">
         <v>0</v>
@@ -16436,13 +16954,13 @@
         <v>656</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="E406" s="4" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="F406" s="7">
         <v>200</v>
@@ -16459,13 +16977,13 @@
         <v>656</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="E407" s="4" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="F407" s="7">
         <v>0</v>
@@ -16482,13 +17000,13 @@
         <v>656</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="E408" s="4" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F408" s="7">
         <v>0</v>
@@ -16505,13 +17023,13 @@
         <v>8</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="F409" s="7">
         <v>0</v>
@@ -16528,13 +17046,13 @@
         <v>8</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="E410" s="4" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="F410" s="7">
         <v>0</v>
@@ -16551,13 +17069,13 @@
         <v>8</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="E411" s="4" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F411" s="7">
         <v>0</v>
@@ -16574,11 +17092,11 @@
         <v>8</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="D412" s="3"/>
       <c r="E412" s="4" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="F412" s="7">
         <v>20</v>
@@ -16595,11 +17113,11 @@
         <v>8</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="D413" s="3"/>
       <c r="E413" s="4" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="F413" s="7">
         <v>20</v>
@@ -16616,11 +17134,11 @@
         <v>8</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="D414" s="3"/>
       <c r="E414" s="4" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="F414" s="7">
         <v>0</v>
@@ -16637,11 +17155,11 @@
         <v>8</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="D415" s="3"/>
       <c r="E415" s="4" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="F415" s="7">
         <v>0</v>
@@ -16658,11 +17176,11 @@
         <v>8</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="D416" s="3"/>
       <c r="E416" s="4" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="F416" s="7">
         <v>0</v>
@@ -16679,11 +17197,11 @@
         <v>8</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D417" s="3"/>
       <c r="E417" s="4" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="F417" s="7">
         <v>0</v>
@@ -16700,11 +17218,11 @@
         <v>8</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="D418" s="3"/>
       <c r="E418" s="4" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="F418" s="7">
         <v>0</v>
@@ -16721,11 +17239,11 @@
         <v>8</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="D419" s="3"/>
       <c r="E419" s="4" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="F419" s="7">
         <v>0</v>
@@ -16742,11 +17260,11 @@
         <v>8</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="D420" s="3"/>
       <c r="E420" s="4" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F420" s="7">
         <v>0</v>
@@ -16763,11 +17281,11 @@
         <v>8</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="D421" s="3"/>
       <c r="E421" s="4" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="F421" s="7">
         <v>0</v>
@@ -16785,11 +17303,11 @@
         <v>8</v>
       </c>
       <c r="C422" s="12" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D422" s="3"/>
       <c r="E422" s="4" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="F422" s="7">
         <v>0</v>
@@ -16800,18 +17318,18 @@
     </row>
     <row r="423" spans="1:7">
       <c r="A423" s="1">
-        <f t="shared" ref="A423:A431" si="0">A422+1</f>
+        <f t="shared" ref="A423:A486" si="0">A422+1</f>
         <v>421</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C423" s="12" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="D423" s="3"/>
       <c r="E423" s="4" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="F423" s="7">
         <v>0</v>
@@ -16829,11 +17347,11 @@
         <v>8</v>
       </c>
       <c r="C424" s="12" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D424" s="3"/>
       <c r="E424" s="4" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="F424" s="7">
         <v>0</v>
@@ -16851,11 +17369,11 @@
         <v>8</v>
       </c>
       <c r="C425" s="12" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="D425" s="3"/>
       <c r="E425" s="4" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="F425" s="7">
         <v>0</v>
@@ -16873,11 +17391,11 @@
         <v>8</v>
       </c>
       <c r="C426" s="12" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="D426" s="3"/>
       <c r="E426" s="4" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="F426" s="7">
         <v>0</v>
@@ -16895,11 +17413,11 @@
         <v>8</v>
       </c>
       <c r="C427" s="12" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D427" s="3"/>
       <c r="E427" s="4" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="F427" s="7">
         <v>0</v>
@@ -16917,11 +17435,11 @@
         <v>8</v>
       </c>
       <c r="C428" s="12" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="D428" s="3"/>
       <c r="E428" s="4" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F428" s="7">
         <v>0</v>
@@ -16939,11 +17457,11 @@
         <v>8</v>
       </c>
       <c r="C429" s="12" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="D429" s="3"/>
       <c r="E429" s="4" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F429" s="7">
         <v>0</v>
@@ -16961,11 +17479,11 @@
         <v>8</v>
       </c>
       <c r="C430" s="12" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="D430" s="3"/>
       <c r="E430" s="4" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="F430" s="7">
         <v>0</v>
@@ -16983,11 +17501,11 @@
         <v>8</v>
       </c>
       <c r="C431" s="12" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="D431" s="3"/>
       <c r="E431" s="4" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F431" s="7">
         <v>0</v>
@@ -16996,285 +17514,1763 @@
         <v>0</v>
       </c>
     </row>
+    <row r="432" spans="1:7">
+      <c r="A432" s="1">
+        <f t="shared" si="0"/>
+        <v>430</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C432" s="12" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D432" s="3"/>
+      <c r="E432" s="13" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F432" s="7">
+        <v>358</v>
+      </c>
+      <c r="G432" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7">
+      <c r="A433" s="1">
+        <f t="shared" si="0"/>
+        <v>431</v>
+      </c>
+      <c r="B433" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C433" s="12" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D433" s="3"/>
+      <c r="E433" s="13" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F433" s="7">
+        <v>0</v>
+      </c>
+      <c r="G433" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7">
+      <c r="A434" s="1">
+        <f t="shared" si="0"/>
+        <v>432</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C434" s="12" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D434" s="3"/>
+      <c r="E434" s="13" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F434" s="7">
+        <v>0</v>
+      </c>
+      <c r="G434" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7">
+      <c r="A435" s="1">
+        <f t="shared" si="0"/>
+        <v>433</v>
+      </c>
+      <c r="B435" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C435" s="12" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D435" s="3"/>
+      <c r="E435" s="13" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F435" s="7">
+        <v>0</v>
+      </c>
+      <c r="G435" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7">
+      <c r="A436" s="1">
+        <f t="shared" si="0"/>
+        <v>434</v>
+      </c>
+      <c r="B436" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C436" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D436" s="3"/>
+      <c r="E436" s="13" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F436" s="7">
+        <v>0</v>
+      </c>
+      <c r="G436" s="7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7">
+      <c r="A437" s="1">
+        <f t="shared" si="0"/>
+        <v>435</v>
+      </c>
+      <c r="B437" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C437" s="12" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E437" s="13" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F437" s="7">
+        <v>0</v>
+      </c>
+      <c r="G437" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7">
+      <c r="A438" s="1">
+        <f t="shared" si="0"/>
+        <v>436</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C438" s="12" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D438" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="E438" s="13" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F438" s="7">
+        <v>0</v>
+      </c>
+      <c r="G438" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7">
+      <c r="A439" s="1">
+        <f t="shared" si="0"/>
+        <v>437</v>
+      </c>
+      <c r="B439" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C439" s="12" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D439" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E439" s="13" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F439" s="7">
+        <v>0</v>
+      </c>
+      <c r="G439" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7">
+      <c r="A440" s="1">
+        <f t="shared" si="0"/>
+        <v>438</v>
+      </c>
+      <c r="B440" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C440" s="12" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D440" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E440" s="13" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F440" s="7">
+        <v>0</v>
+      </c>
+      <c r="G440" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7">
+      <c r="A441" s="1">
+        <f t="shared" si="0"/>
+        <v>439</v>
+      </c>
+      <c r="B441" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C441" s="12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D441" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E441" s="13" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F441" s="7">
+        <v>0</v>
+      </c>
+      <c r="G441" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7">
+      <c r="A442" s="1">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C442" s="12" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D442" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E442" s="13" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F442" s="7">
+        <v>0</v>
+      </c>
+      <c r="G442" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7">
+      <c r="A443" s="1">
+        <f t="shared" si="0"/>
+        <v>441</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C443" s="12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D443" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E443" s="13" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F443" s="7">
+        <v>0</v>
+      </c>
+      <c r="G443" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7">
+      <c r="A444" s="1">
+        <f t="shared" si="0"/>
+        <v>442</v>
+      </c>
+      <c r="B444" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C444" s="12" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D444" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E444" s="13" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F444" s="7">
+        <v>0</v>
+      </c>
+      <c r="G444" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445" spans="1:7">
+      <c r="A445" s="1">
+        <f t="shared" si="0"/>
+        <v>443</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C445" s="12" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D445" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E445" s="13" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F445" s="7">
+        <v>0</v>
+      </c>
+      <c r="G445" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446" spans="1:7">
+      <c r="A446" s="1">
+        <f t="shared" si="0"/>
+        <v>444</v>
+      </c>
+      <c r="B446" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C446" s="12" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D446" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E446" s="13" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F446" s="7">
+        <v>0</v>
+      </c>
+      <c r="G446" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447" spans="1:7">
+      <c r="A447" s="1">
+        <f t="shared" si="0"/>
+        <v>445</v>
+      </c>
+      <c r="B447" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C447" s="12" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D447" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E447" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F447" s="7">
+        <v>0</v>
+      </c>
+      <c r="G447" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448" spans="1:7">
+      <c r="A448" s="1">
+        <f t="shared" si="0"/>
+        <v>446</v>
+      </c>
+      <c r="B448" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C448" s="12" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D448" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E448" s="13" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F448" s="7">
+        <v>0</v>
+      </c>
+      <c r="G448" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449" spans="1:7">
+      <c r="A449" s="1">
+        <f t="shared" si="0"/>
+        <v>447</v>
+      </c>
+      <c r="B449" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C449" s="12" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D449" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E449" s="13" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F449" s="7">
+        <v>0</v>
+      </c>
+      <c r="G449" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450" spans="1:7">
+      <c r="A450" s="1">
+        <f t="shared" si="0"/>
+        <v>448</v>
+      </c>
+      <c r="B450" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C450" s="12" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D450" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E450" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F450" s="7">
+        <v>0</v>
+      </c>
+      <c r="G450" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451" spans="1:7">
+      <c r="A451" s="1">
+        <f t="shared" si="0"/>
+        <v>449</v>
+      </c>
+      <c r="B451" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C451" s="12" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D451" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E451" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="F451" s="7">
+        <v>0</v>
+      </c>
+      <c r="G451" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:7">
+      <c r="A452" s="1">
+        <f t="shared" si="0"/>
+        <v>450</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C452" s="12" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D452" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E452" s="13" t="s">
+        <v>1409</v>
+      </c>
+      <c r="F452" s="7">
+        <v>0</v>
+      </c>
+      <c r="G452" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453" spans="1:7">
+      <c r="A453" s="1">
+        <f t="shared" si="0"/>
+        <v>451</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C453" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D453" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E453" s="13" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F453" s="7">
+        <v>0</v>
+      </c>
+      <c r="G453" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454" spans="1:7">
+      <c r="A454" s="1">
+        <f t="shared" si="0"/>
+        <v>452</v>
+      </c>
+      <c r="B454" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C454" s="12" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D454" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="E454" s="13" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F454" s="7">
+        <v>0</v>
+      </c>
+      <c r="G454" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455" spans="1:7">
+      <c r="A455" s="1">
+        <f t="shared" si="0"/>
+        <v>453</v>
+      </c>
+      <c r="B455" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C455" s="12" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D455" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E455" s="13" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F455" s="7">
+        <v>0</v>
+      </c>
+      <c r="G455" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456" spans="1:7">
+      <c r="A456" s="1">
+        <f t="shared" si="0"/>
+        <v>454</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C456" s="12" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D456" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E456" s="13" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F456" s="7">
+        <v>0</v>
+      </c>
+      <c r="G456" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457" spans="1:7">
+      <c r="A457" s="1">
+        <f t="shared" si="0"/>
+        <v>455</v>
+      </c>
+      <c r="B457" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C457" s="12" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D457" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E457" s="13" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F457" s="7">
+        <v>0</v>
+      </c>
+      <c r="G457" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458" spans="1:7">
+      <c r="A458" s="1">
+        <f t="shared" si="0"/>
+        <v>456</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C458" s="12" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D458" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E458" s="13" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F458" s="7">
+        <v>0</v>
+      </c>
+      <c r="G458" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459" spans="1:7">
+      <c r="A459" s="1">
+        <f t="shared" si="0"/>
+        <v>457</v>
+      </c>
+      <c r="B459" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C459" s="12" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D459" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E459" s="13" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F459" s="7">
+        <v>0</v>
+      </c>
+      <c r="G459" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460" spans="1:7">
+      <c r="A460" s="1">
+        <f t="shared" si="0"/>
+        <v>458</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C460" s="12" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D460" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E460" s="13" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F460" s="7">
+        <v>0</v>
+      </c>
+      <c r="G460" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461" spans="1:7">
+      <c r="A461" s="1">
+        <f t="shared" si="0"/>
+        <v>459</v>
+      </c>
+      <c r="B461" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C461" s="12" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D461" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E461" s="13" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F461" s="7">
+        <v>0</v>
+      </c>
+      <c r="G461" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462" spans="1:7">
+      <c r="A462" s="1">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+      <c r="B462" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C462" s="12" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D462" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E462" s="13" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F462" s="7">
+        <v>0</v>
+      </c>
+      <c r="G462" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463" spans="1:7">
+      <c r="A463" s="1">
+        <f t="shared" si="0"/>
+        <v>461</v>
+      </c>
+      <c r="B463" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C463" s="12" t="s">
+        <v>1347</v>
+      </c>
+      <c r="D463" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="E463" s="13" t="s">
+        <v>1420</v>
+      </c>
+      <c r="F463" s="7">
+        <v>0</v>
+      </c>
+      <c r="G463" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464" spans="1:7">
+      <c r="A464" s="1">
+        <f t="shared" si="0"/>
+        <v>462</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C464" s="12" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D464" s="3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E464" s="13" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F464" s="7">
+        <v>0</v>
+      </c>
+      <c r="G464" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7">
+      <c r="A465" s="1">
+        <f t="shared" si="0"/>
+        <v>463</v>
+      </c>
+      <c r="B465" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C465" s="12" t="s">
+        <v>1351</v>
+      </c>
+      <c r="D465" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E465" s="13" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F465" s="7">
+        <v>0</v>
+      </c>
+      <c r="G465" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7">
+      <c r="A466" s="1">
+        <f t="shared" si="0"/>
+        <v>464</v>
+      </c>
+      <c r="B466" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C466" s="12" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D466" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E466" s="13" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F466" s="7">
+        <v>0</v>
+      </c>
+      <c r="G466" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7">
+      <c r="A467" s="1">
+        <f t="shared" si="0"/>
+        <v>465</v>
+      </c>
+      <c r="B467" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C467" s="12" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D467" s="3" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E467" s="13" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F467" s="7">
+        <v>0</v>
+      </c>
+      <c r="G467" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7">
+      <c r="A468" s="1">
+        <f t="shared" si="0"/>
+        <v>466</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C468" s="12" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D468" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E468" s="13" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F468" s="7">
+        <v>0</v>
+      </c>
+      <c r="G468" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7">
+      <c r="A469" s="1">
+        <f t="shared" si="0"/>
+        <v>467</v>
+      </c>
+      <c r="B469" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C469" s="12" t="s">
+        <v>1359</v>
+      </c>
+      <c r="D469" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E469" s="13" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F469" s="7">
+        <v>0</v>
+      </c>
+      <c r="G469" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7">
+      <c r="A470" s="1">
+        <f t="shared" si="0"/>
+        <v>468</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C470" s="12" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D470" s="3" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E470" s="13" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F470" s="7">
+        <v>0</v>
+      </c>
+      <c r="G470" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7">
+      <c r="A471" s="1">
+        <f t="shared" si="0"/>
+        <v>469</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C471" s="12" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D471" s="3" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E471" s="13" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F471" s="7">
+        <v>0</v>
+      </c>
+      <c r="G471" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7">
+      <c r="A472" s="1">
+        <f t="shared" si="0"/>
+        <v>470</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C472" s="12" t="s">
+        <v>1365</v>
+      </c>
+      <c r="D472" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E472" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F472" s="7">
+        <v>0</v>
+      </c>
+      <c r="G472" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7">
+      <c r="A473" s="1">
+        <f t="shared" si="0"/>
+        <v>471</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C473" s="12" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D473" s="3" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E473" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F473" s="7">
+        <v>0</v>
+      </c>
+      <c r="G473" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7">
+      <c r="A474" s="1">
+        <f t="shared" si="0"/>
+        <v>472</v>
+      </c>
+      <c r="B474" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C474" s="12" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D474" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E474" s="13" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F474" s="7">
+        <v>0</v>
+      </c>
+      <c r="G474" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7">
+      <c r="A475" s="1">
+        <f t="shared" si="0"/>
+        <v>473</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C475" s="12" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D475" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E475" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="F475" s="7">
+        <v>0</v>
+      </c>
+      <c r="G475" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7">
+      <c r="A476" s="1">
+        <f t="shared" si="0"/>
+        <v>474</v>
+      </c>
+      <c r="B476" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C476" s="12" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D476" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E476" s="13" t="s">
+        <v>1429</v>
+      </c>
+      <c r="F476" s="7">
+        <v>0</v>
+      </c>
+      <c r="G476" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7">
+      <c r="A477" s="1">
+        <f t="shared" si="0"/>
+        <v>475</v>
+      </c>
+      <c r="B477" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C477" s="12" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D477" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E477" s="13" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F477" s="7">
+        <v>0</v>
+      </c>
+      <c r="G477" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7">
+      <c r="A478" s="1">
+        <f t="shared" si="0"/>
+        <v>476</v>
+      </c>
+      <c r="B478" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C478" s="12" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D478" s="3" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E478" s="13" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F478" s="7">
+        <v>0</v>
+      </c>
+      <c r="G478" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7">
+      <c r="A479" s="1">
+        <f t="shared" si="0"/>
+        <v>477</v>
+      </c>
+      <c r="B479" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C479" s="12" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D479" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E479" s="13" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F479" s="7">
+        <v>0</v>
+      </c>
+      <c r="G479" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7">
+      <c r="A480" s="1">
+        <f t="shared" si="0"/>
+        <v>478</v>
+      </c>
+      <c r="B480" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C480" s="12" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D480" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E480" s="13" t="s">
+        <v>1433</v>
+      </c>
+      <c r="F480" s="7">
+        <v>0</v>
+      </c>
+      <c r="G480" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:7">
+      <c r="A481" s="1">
+        <f t="shared" si="0"/>
+        <v>479</v>
+      </c>
+      <c r="B481" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C481" s="12" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D481" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E481" s="13" t="s">
+        <v>1434</v>
+      </c>
+      <c r="F481" s="7">
+        <v>0</v>
+      </c>
+      <c r="G481" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482" spans="1:7">
+      <c r="A482" s="1">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="B482" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C482" s="12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D482" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E482" s="13" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F482" s="7">
+        <v>0</v>
+      </c>
+      <c r="G482" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483" spans="1:7">
+      <c r="A483" s="1">
+        <f t="shared" si="0"/>
+        <v>481</v>
+      </c>
+      <c r="B483" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C483" s="12" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D483" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="E483" s="13" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F483" s="7">
+        <v>0</v>
+      </c>
+      <c r="G483" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:7">
+      <c r="A484" s="1">
+        <f t="shared" si="0"/>
+        <v>482</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C484" s="12" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D484" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E484" s="13" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F484" s="7">
+        <v>0</v>
+      </c>
+      <c r="G484" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485" spans="1:7">
+      <c r="A485" s="1">
+        <f t="shared" si="0"/>
+        <v>483</v>
+      </c>
+      <c r="B485" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C485" s="12" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D485" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E485" s="13" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F485" s="7">
+        <v>0</v>
+      </c>
+      <c r="G485" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486" spans="1:7">
+      <c r="A486" s="1">
+        <f t="shared" si="0"/>
+        <v>484</v>
+      </c>
+      <c r="B486" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C486" s="12" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D486" s="3" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E486" s="13" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F486" s="7">
+        <v>0</v>
+      </c>
+      <c r="G486" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="487" spans="1:7">
+      <c r="A487" s="1">
+        <f t="shared" ref="A487:A493" si="1">A486+1</f>
+        <v>485</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C487" s="12" t="s">
+        <v>1395</v>
+      </c>
+      <c r="D487" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E487" s="13" t="s">
+        <v>1440</v>
+      </c>
+      <c r="F487" s="7">
+        <v>0</v>
+      </c>
+      <c r="G487" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="488" spans="1:7">
+      <c r="A488" s="1">
+        <f t="shared" si="1"/>
+        <v>486</v>
+      </c>
+      <c r="B488" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C488" s="12" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D488" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E488" s="13" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F488" s="7">
+        <v>0</v>
+      </c>
+      <c r="G488" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="489" spans="1:7">
+      <c r="A489" s="1">
+        <f t="shared" si="1"/>
+        <v>487</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C489" s="12" t="s">
+        <v>1399</v>
+      </c>
+      <c r="D489" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E489" s="13" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F489" s="7">
+        <v>0</v>
+      </c>
+      <c r="G489" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490" spans="1:7">
+      <c r="A490" s="1">
+        <f t="shared" si="1"/>
+        <v>488</v>
+      </c>
+      <c r="B490" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C490" s="12" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D490" s="3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E490" s="13" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F490" s="7">
+        <v>0</v>
+      </c>
+      <c r="G490" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491" spans="1:7">
+      <c r="A491" s="1">
+        <f t="shared" si="1"/>
+        <v>489</v>
+      </c>
+      <c r="B491" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C491" s="12" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D491" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E491" s="13" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F491" s="7">
+        <v>0</v>
+      </c>
+      <c r="G491" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492" spans="1:7">
+      <c r="A492" s="1">
+        <f t="shared" si="1"/>
+        <v>490</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C492" s="12" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D492" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E492" s="13" t="s">
+        <v>1445</v>
+      </c>
+      <c r="F492" s="7">
+        <v>0</v>
+      </c>
+      <c r="G492" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493" spans="1:7">
+      <c r="A493" s="1">
+        <f t="shared" si="1"/>
+        <v>491</v>
+      </c>
+      <c r="B493" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C493" s="12" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D493" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E493" s="13" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F493" s="7">
+        <v>0</v>
+      </c>
+      <c r="G493" s="7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I431" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}"/>
+  <autoFilter ref="A2:I493" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}"/>
   <conditionalFormatting sqref="C2:C153 C155:C359">
-    <cfRule type="duplicateValues" dxfId="195" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C223">
-    <cfRule type="duplicateValues" dxfId="194" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C241:C243">
-    <cfRule type="duplicateValues" dxfId="193" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C292">
-    <cfRule type="duplicateValues" dxfId="191" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="246" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="247" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="264" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="265" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C331:C334">
-    <cfRule type="duplicateValues" dxfId="183" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="duplicateValues" dxfId="182" priority="164" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="163" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="162" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="182" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="181" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="180" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
-    <cfRule type="duplicateValues" dxfId="177" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="167" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="168" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="169" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="185" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="186" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="187" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E62 E2 E23:E30 E8:E21">
-    <cfRule type="duplicateValues" dxfId="172" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="187" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="205" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E62 E23:E30 E8:E21">
-    <cfRule type="duplicateValues" dxfId="170" priority="189" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E57">
-    <cfRule type="duplicateValues" dxfId="168" priority="185" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="203" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E112">
-    <cfRule type="duplicateValues" dxfId="167" priority="154" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="153" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="152" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="172" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="171" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="170" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E113:E115 E90:E111 E63:E65">
-    <cfRule type="duplicateValues" dxfId="162" priority="259" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="277" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E113:E115">
-    <cfRule type="duplicateValues" dxfId="160" priority="265" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="283" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E116:E141">
-    <cfRule type="duplicateValues" dxfId="158" priority="136" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="135" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="134" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="154" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="153" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="152" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E156:E166">
-    <cfRule type="duplicateValues" dxfId="153" priority="121" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="120" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="119" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="139" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="138" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="137" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E167:E171 E173:E174">
-    <cfRule type="duplicateValues" dxfId="148" priority="115" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="116" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="114" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="133" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="134" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="132" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="143" priority="174" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="172" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="173" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="192" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="190" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="191" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175:E182">
-    <cfRule type="duplicateValues" dxfId="138" priority="109" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="111" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="110" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="127" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="129" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="128" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E183">
-    <cfRule type="duplicateValues" dxfId="133" priority="106" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="104" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="105" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="124" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="122" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="123" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E184:E189">
-    <cfRule type="duplicateValues" dxfId="130" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="157" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="159" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="158" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="175" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="177" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="176" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E207:E220">
-    <cfRule type="duplicateValues" dxfId="125" priority="103" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="101" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="102" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="121" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="119" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="120" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E221:E222">
-    <cfRule type="duplicateValues" dxfId="120" priority="256" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="255" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="254" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="274" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="273" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="272" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E223:E228">
-    <cfRule type="duplicateValues" dxfId="115" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E236:E240">
-    <cfRule type="duplicateValues" dxfId="114" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="93" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="92" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="91" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="111" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="110" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="109" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E244:E247">
-    <cfRule type="duplicateValues" dxfId="109" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="88" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="86" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="87" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="104" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="105" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E248:E253">
-    <cfRule type="duplicateValues" dxfId="104" priority="81" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="83" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="82" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="99" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="100" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E255">
-    <cfRule type="duplicateValues" dxfId="99" priority="184" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="183" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="182" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="202" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="201" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="200" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E256:E261">
-    <cfRule type="duplicateValues" dxfId="94" priority="73" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="71" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="72" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="91" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="89" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="90" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E262:E267">
-    <cfRule type="duplicateValues" dxfId="89" priority="66" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="67" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="68" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="84" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="85" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="86" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E268:E282">
-    <cfRule type="duplicateValues" dxfId="84" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="61" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="62" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="63" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="79" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="80" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="81" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E283:E292">
-    <cfRule type="duplicateValues" dxfId="79" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="58" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="57" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="76" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="75" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E293:E296">
-    <cfRule type="duplicateValues" dxfId="71" priority="49" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="50" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="67" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="68" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E297:E298">
-    <cfRule type="duplicateValues" dxfId="63" priority="210" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="228" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E305:E309">
-    <cfRule type="duplicateValues" dxfId="59" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="214" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="232" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E310:E315">
-    <cfRule type="duplicateValues" dxfId="55" priority="225" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="224" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="243" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="242" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E316:E327">
-    <cfRule type="duplicateValues" dxfId="47" priority="231"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="238" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="237" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="255" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E328">
-    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="42" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="41" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E329">
-    <cfRule type="duplicateValues" dxfId="31" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="33" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="34" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="52" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E330">
-    <cfRule type="duplicateValues" dxfId="23" priority="26" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="25" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="43" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E332:E358">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="10" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="9" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="28" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E360:E431">
-    <cfRule type="duplicateValues" dxfId="7" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="18" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="17" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  <conditionalFormatting sqref="E360:E493">
+    <cfRule type="duplicateValues" dxfId="7" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="36" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="35" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Cambium_Import_Details.xlsx
+++ b/Cambium_Import_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\czad\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A466FEB1-298C-499F-9BDE-5CED6828A4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB60CAB4-B0CB-4553-AE52-C350FC0A7514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{42E993CD-9B70-4509-B668-6EEF51FEBD70}"/>
   </bookViews>
@@ -21,10 +21,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$492</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -8105,10 +8114,11 @@
         <v>63</v>
       </c>
       <c r="F21" s="7">
-        <v>496</v>
+        <f>496+1000</f>
+        <v>1496</v>
       </c>
       <c r="G21" s="7">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -8542,7 +8552,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G40" s="7">
         <v>1000</v>
@@ -8796,11 +8806,10 @@
         <v>153</v>
       </c>
       <c r="F51" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G51" s="7">
-        <f>VLOOKUP(C51,'[1]Open Order'!$A:$E,5,0)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -15998,10 +16007,10 @@
         <v>1094</v>
       </c>
       <c r="F364" s="7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G364" s="7">
-        <v>140</v>
+        <v>100</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -16021,10 +16030,10 @@
         <v>1097</v>
       </c>
       <c r="F365" s="7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G365" s="7">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -17010,10 +17019,10 @@
         <v>1194</v>
       </c>
       <c r="F408" s="7">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G408" s="7">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409" spans="1:7">

--- a/Cambium_Import_Details.xlsx
+++ b/Cambium_Import_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rusha\Downloads\Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3657AC-7AE1-4D12-B6F8-4077A65D7FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C2FCA5-D5A8-4C2E-B85E-B4773614115C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42E993CD-9B70-4509-B668-6EEF51FEBD70}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$493</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$494</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1456">
   <si>
     <t>SR NO</t>
   </si>
@@ -4409,7 +4409,13 @@
     <t>30-06-2026 &amp; 03-07-2026</t>
   </si>
   <si>
-    <t>500 CBU &amp; 250 CKD</t>
+    <t>AI-04 Pro</t>
+  </si>
+  <si>
+    <t>FBA80181</t>
+  </si>
+  <si>
+    <t>800 CBU &amp; 250 CKD</t>
   </si>
 </sst>
 </file>
@@ -4573,7 +4579,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4627,7 +4633,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -7684,30 +7689,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}">
-  <dimension ref="A1:I493"/>
+  <dimension ref="A1:I494"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
     <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="F1" s="9">
-        <f>SUBTOTAL(9,F3:F493)</f>
+        <f>SUBTOTAL(9,F3:F494)</f>
         <v>13791</v>
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="9">
-        <f>SUBTOTAL(9,H3:H493)</f>
-        <v>22600</v>
-      </c>
+        <f>SUBTOTAL(9,H3:H494)</f>
+        <v>40427</v>
+      </c>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
@@ -7839,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="7">
-        <v>0</v>
+        <v>5004</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -7865,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="7">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -8073,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="7">
-        <v>0</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -8099,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <v>0</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -8334,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="7">
-        <v>0</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -8516,7 +8522,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="7">
-        <v>0</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -8750,7 +8756,7 @@
         <v>46206</v>
       </c>
       <c r="H41" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -8985,7 +8991,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="7">
-        <v>0</v>
+        <v>504</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -9454,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -13280,11 +13286,11 @@
         <v>0</v>
       </c>
       <c r="H215" s="7">
-        <f>500+250</f>
-        <v>750</v>
-      </c>
-      <c r="I215" s="23" t="s">
-        <v>1453</v>
+        <f>800+250</f>
+        <v>1050</v>
+      </c>
+      <c r="I215" t="s">
+        <v>1455</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -17002,7 +17008,7 @@
         <v>0</v>
       </c>
       <c r="H358" s="7">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="359" spans="1:8">
@@ -18146,7 +18152,8 @@
         <v>0</v>
       </c>
       <c r="H402" s="7">
-        <v>1004</v>
+        <f>1004+2000</f>
+        <v>3004</v>
       </c>
     </row>
     <row r="403" spans="1:8">
@@ -20356,7 +20363,7 @@
     </row>
     <row r="487" spans="1:8">
       <c r="A487" s="1">
-        <f t="shared" ref="A487:A493" si="1">A486+1</f>
+        <f t="shared" ref="A487:A494" si="1">A486+1</f>
         <v>485</v>
       </c>
       <c r="B487" s="1" t="s">
@@ -20543,8 +20550,33 @@
         <v>0</v>
       </c>
     </row>
+    <row r="494" spans="1:8">
+      <c r="A494" s="1">
+        <f t="shared" si="1"/>
+        <v>492</v>
+      </c>
+      <c r="B494" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C494" s="11" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D494" s="3"/>
+      <c r="E494" s="11" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F494" s="7">
+        <v>0</v>
+      </c>
+      <c r="G494" s="7">
+        <v>0</v>
+      </c>
+      <c r="H494" s="7">
+        <v>1000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I493" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}"/>
+  <autoFilter ref="A2:I494" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}"/>
   <conditionalFormatting sqref="C2:C153 C155:C359">
     <cfRule type="duplicateValues" dxfId="195" priority="285"/>
   </conditionalFormatting>
@@ -20813,7 +20845,7 @@
     <cfRule type="duplicateValues" dxfId="9" priority="27" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="8" priority="28" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E360 E362:E493">
+  <conditionalFormatting sqref="E360 E362:E494">
     <cfRule type="duplicateValues" dxfId="7" priority="29"/>
     <cfRule type="duplicateValues" dxfId="6" priority="30"/>
     <cfRule type="duplicateValues" dxfId="5" priority="31"/>

--- a/Cambium_Import_Details.xlsx
+++ b/Cambium_Import_Details.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rusha\Downloads\Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C2FCA5-D5A8-4C2E-B85E-B4773614115C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FA0F24-729E-416B-819D-0A07BEFC7F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{42E993CD-9B70-4509-B668-6EEF51FEBD70}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$494</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$I$495</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1957" uniqueCount="1456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="1458">
   <si>
     <t>SR NO</t>
   </si>
@@ -4406,9 +4406,6 @@
     <t>AC-6XL</t>
   </si>
   <si>
-    <t>30-06-2026 &amp; 03-07-2026</t>
-  </si>
-  <si>
     <t>AI-04 Pro</t>
   </si>
   <si>
@@ -4416,6 +4413,15 @@
   </si>
   <si>
     <t>800 CBU &amp; 250 CKD</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>SP-02</t>
+  </si>
+  <si>
+    <t>FBA80215</t>
   </si>
 </sst>
 </file>
@@ -4642,6 +4648,140 @@
   <dxfs count="196">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <condense val="0"/>
         <extend val="0"/>
         <color rgb="FF9C0006"/>
@@ -4716,6 +4856,364 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4906,38 +5404,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4992,466 +5458,6 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -6522,20 +6528,6 @@
     </dxf>
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -6566,6 +6558,20 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -7689,7 +7695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}">
-  <dimension ref="A1:I494"/>
+  <dimension ref="A1:I495"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -7705,13 +7711,13 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="F1" s="9">
-        <f>SUBTOTAL(9,F3:F494)</f>
-        <v>13791</v>
+        <f>SUBTOTAL(9,F3:F495)</f>
+        <v>3390</v>
       </c>
       <c r="G1" s="9"/>
       <c r="H1" s="9">
-        <f>SUBTOTAL(9,H3:H494)</f>
-        <v>40427</v>
+        <f>SUBTOTAL(9,H3:H495)</f>
+        <v>48871</v>
       </c>
       <c r="I1" s="10"/>
     </row>
@@ -8255,11 +8261,10 @@
         <v>63</v>
       </c>
       <c r="F22" s="7">
-        <f>496+1000</f>
-        <v>1496</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>1452</v>
+        <v>1000</v>
+      </c>
+      <c r="G22" s="13">
+        <v>46211</v>
       </c>
       <c r="H22" s="7">
         <v>0</v>
@@ -8753,7 +8758,7 @@
         <v>1000</v>
       </c>
       <c r="G41" s="13">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="H41" s="7">
         <v>1000</v>
@@ -9040,7 +9045,7 @@
         <v>1000</v>
       </c>
       <c r="G52" s="13">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="H52" s="7">
         <v>0</v>
@@ -9460,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="7">
-        <v>1000</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -10650,10 +10655,10 @@
         <v>339</v>
       </c>
       <c r="F114" s="7">
-        <v>504</v>
-      </c>
-      <c r="G114" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G114" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H114" s="7">
         <v>0</v>
@@ -11301,10 +11306,10 @@
         <v>415</v>
       </c>
       <c r="F139" s="7">
-        <v>2000</v>
-      </c>
-      <c r="G139" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G139" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H139" s="8">
         <v>0</v>
@@ -11639,10 +11644,10 @@
         <v>454</v>
       </c>
       <c r="F152" s="7">
-        <v>2000</v>
-      </c>
-      <c r="G152" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G152" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H152" s="7">
         <v>2000</v>
@@ -11983,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="H165" s="7">
-        <v>0</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -12578,10 +12583,10 @@
         <v>562</v>
       </c>
       <c r="F188" s="7">
-        <v>2000</v>
-      </c>
-      <c r="G188" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G188" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H188" s="7">
         <v>0</v>
@@ -13290,7 +13295,7 @@
         <v>1050</v>
       </c>
       <c r="I215" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="216" spans="1:9">
@@ -16222,13 +16227,14 @@
         <v>984</v>
       </c>
       <c r="F328" s="7">
-        <v>996</v>
-      </c>
-      <c r="G328" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G328" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H328" s="8">
-        <v>1002</v>
+        <f>1002+1002</f>
+        <v>2004</v>
       </c>
     </row>
     <row r="329" spans="1:8">
@@ -17080,13 +17086,13 @@
         <v>1083</v>
       </c>
       <c r="F361" s="7">
-        <v>1300</v>
-      </c>
-      <c r="G361" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G361" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H361" s="7">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="362" spans="1:8">
@@ -17106,10 +17112,10 @@
         <v>1445</v>
       </c>
       <c r="F362" s="18">
-        <v>200</v>
-      </c>
-      <c r="G362" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G362" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H362" s="7">
         <v>400</v>
@@ -17187,7 +17193,7 @@
         <v>40</v>
       </c>
       <c r="G365" s="13">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="H365" s="7">
         <v>100</v>
@@ -17213,7 +17219,7 @@
         <v>50</v>
       </c>
       <c r="G366" s="13">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="H366" s="7">
         <v>100</v>
@@ -17236,13 +17242,14 @@
         <v>1099</v>
       </c>
       <c r="F367" s="18">
-        <v>300</v>
-      </c>
-      <c r="G367" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G367" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H367" s="7">
-        <v>100</v>
+        <f>100+500</f>
+        <v>600</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -17262,13 +17269,13 @@
         <v>1102</v>
       </c>
       <c r="F368" s="7">
+        <v>0</v>
+      </c>
+      <c r="G368" s="13" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H368" s="20">
         <v>200</v>
-      </c>
-      <c r="G368" s="13">
-        <v>46203</v>
-      </c>
-      <c r="H368" s="20">
-        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:8">
@@ -17320,7 +17327,7 @@
         <v>0</v>
       </c>
       <c r="H370" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="371" spans="1:8">
@@ -17444,10 +17451,10 @@
         <v>1123</v>
       </c>
       <c r="F375" s="7">
-        <v>405</v>
-      </c>
-      <c r="G375" s="13">
-        <v>46203</v>
+        <v>0</v>
+      </c>
+      <c r="G375" s="13" t="s">
+        <v>1455</v>
       </c>
       <c r="H375" s="7">
         <v>0</v>
@@ -18179,7 +18186,7 @@
         <v>0</v>
       </c>
       <c r="H403" s="7">
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="404" spans="1:8">
@@ -18205,7 +18212,7 @@
         <v>0</v>
       </c>
       <c r="H404" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="405" spans="1:8">
@@ -18309,7 +18316,7 @@
         <v>0</v>
       </c>
       <c r="H408" s="7">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="409" spans="1:8">
@@ -18332,7 +18339,7 @@
         <v>300</v>
       </c>
       <c r="G409" s="13">
-        <v>46206</v>
+        <v>46211</v>
       </c>
       <c r="H409" s="7">
         <v>0</v>
@@ -20363,7 +20370,7 @@
     </row>
     <row r="487" spans="1:8">
       <c r="A487" s="1">
-        <f t="shared" ref="A487:A494" si="1">A486+1</f>
+        <f t="shared" ref="A487:A495" si="1">A486+1</f>
         <v>485</v>
       </c>
       <c r="B487" s="1" t="s">
@@ -20559,11 +20566,11 @@
         <v>8</v>
       </c>
       <c r="C494" s="11" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="D494" s="3"/>
       <c r="E494" s="11" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="F494" s="7">
         <v>0</v>
@@ -20575,8 +20582,33 @@
         <v>1000</v>
       </c>
     </row>
+    <row r="495" spans="1:8">
+      <c r="A495" s="1">
+        <f t="shared" si="1"/>
+        <v>493</v>
+      </c>
+      <c r="B495" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C495" s="11" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D495" s="3"/>
+      <c r="E495" s="11" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F495" s="7">
+        <v>0</v>
+      </c>
+      <c r="G495" s="7">
+        <v>0</v>
+      </c>
+      <c r="H495" s="7">
+        <v>500</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I494" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}"/>
+  <autoFilter ref="A2:I495" xr:uid="{2638B9F0-C254-4E3B-92A1-1C14FA755F6E}"/>
   <conditionalFormatting sqref="C2:C153 C155:C359">
     <cfRule type="duplicateValues" dxfId="195" priority="285"/>
   </conditionalFormatting>
@@ -20588,24 +20620,24 @@
     <cfRule type="duplicateValues" dxfId="192" priority="269"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C292">
-    <cfRule type="duplicateValues" dxfId="191" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="264" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="265" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="264" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="265" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="260"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C331:C334">
     <cfRule type="duplicateValues" dxfId="183" priority="257"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22">
-    <cfRule type="duplicateValues" dxfId="182" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="182" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="181" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="180" priority="180" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="181" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="182" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E31">
     <cfRule type="duplicateValues" dxfId="177" priority="183"/>
@@ -20619,136 +20651,136 @@
     <cfRule type="duplicateValues" dxfId="171" priority="205" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E62 E23:E30 E8:E21">
-    <cfRule type="duplicateValues" dxfId="170" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="207" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="206"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E38:E57">
     <cfRule type="duplicateValues" dxfId="168" priority="203" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E112">
-    <cfRule type="duplicateValues" dxfId="167" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="172" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="171" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="165" priority="170" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="171" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="172" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E113:E115 E90:E111 E63:E65">
-    <cfRule type="duplicateValues" dxfId="162" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="277" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="277" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="276"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E113:E115">
-    <cfRule type="duplicateValues" dxfId="160" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="283" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="283" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="282"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E116:E141">
-    <cfRule type="duplicateValues" dxfId="158" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="152" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="153" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="154" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="154" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="153" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="152" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E156:E166">
-    <cfRule type="duplicateValues" dxfId="153" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="139" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="138" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="151" priority="137" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="138" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="139" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E167:E171 E173:E174">
-    <cfRule type="duplicateValues" dxfId="148" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="132" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="133" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="134" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="133" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="134" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="132" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E172">
-    <cfRule type="duplicateValues" dxfId="143" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="190" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="191" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="192" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="192" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="190" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="191" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E175:E182">
-    <cfRule type="duplicateValues" dxfId="138" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="127" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="128" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="129" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="127" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="129" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="128" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E183">
-    <cfRule type="duplicateValues" dxfId="133" priority="122" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="123" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="124" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="124" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="122" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="123" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E184:E189">
-    <cfRule type="duplicateValues" dxfId="130" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="175" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="175" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="177" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="127" priority="176" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="177" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="173"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E207:E220">
-    <cfRule type="duplicateValues" dxfId="125" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="121" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="117"/>
     <cfRule type="duplicateValues" dxfId="123" priority="119" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="122" priority="120" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="121" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E221:E222">
-    <cfRule type="duplicateValues" dxfId="120" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="274" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="273" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="118" priority="272" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="273" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="274" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="270"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E223:E228">
     <cfRule type="duplicateValues" dxfId="115" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E236:E240">
-    <cfRule type="duplicateValues" dxfId="114" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="109" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="111" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="111" priority="110" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="111" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="109" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E244:E247">
     <cfRule type="duplicateValues" dxfId="109" priority="102"/>
     <cfRule type="duplicateValues" dxfId="108" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="104" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="105" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="104" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="105" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E248:E253">
-    <cfRule type="duplicateValues" dxfId="104" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="99" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="100" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="99" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="101" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="100" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="98"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E255">
-    <cfRule type="duplicateValues" dxfId="99" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="202" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="201" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="97" priority="200" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="201" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="202" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E256:E261">
-    <cfRule type="duplicateValues" dxfId="94" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="89" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="90" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="91" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="91" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="89" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="90" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E262:E267">
-    <cfRule type="duplicateValues" dxfId="89" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="84" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="88" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="84" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="82"/>
     <cfRule type="duplicateValues" dxfId="86" priority="85" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="85" priority="86" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E268:E282">
-    <cfRule type="duplicateValues" dxfId="84" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="77"/>
     <cfRule type="duplicateValues" dxfId="82" priority="79" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="81" priority="80" stopIfTrue="1"/>
     <cfRule type="duplicateValues" dxfId="80" priority="81" stopIfTrue="1"/>
@@ -20756,21 +20788,21 @@
   <conditionalFormatting sqref="E283:E292">
     <cfRule type="duplicateValues" dxfId="79" priority="69"/>
     <cfRule type="duplicateValues" dxfId="78" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="75" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="76" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="76" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="75" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E293:E296">
-    <cfRule type="duplicateValues" dxfId="71" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="67" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="67" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="63"/>
     <cfRule type="duplicateValues" dxfId="64" priority="68" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E297:E298">
@@ -20780,20 +20812,20 @@
     <cfRule type="duplicateValues" dxfId="60" priority="231"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E305:E309">
-    <cfRule type="duplicateValues" dxfId="59" priority="232" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="232" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E310:E315">
-    <cfRule type="duplicateValues" dxfId="55" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="242" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="243" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="243" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="242" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E316:E327">
     <cfRule type="duplicateValues" dxfId="47" priority="249"/>
@@ -20802,58 +20834,58 @@
     <cfRule type="duplicateValues" dxfId="44" priority="252"/>
     <cfRule type="duplicateValues" dxfId="43" priority="253"/>
     <cfRule type="duplicateValues" dxfId="42" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="255" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="256" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="255" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E328">
-    <cfRule type="duplicateValues" dxfId="39" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="59" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="60" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="59" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E329">
-    <cfRule type="duplicateValues" dxfId="31" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="51" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="47"/>
     <cfRule type="duplicateValues" dxfId="24" priority="52" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E330">
-    <cfRule type="duplicateValues" dxfId="23" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="43" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="44" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="43" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E332:E358">
     <cfRule type="duplicateValues" dxfId="15" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="28" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="27" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="26"/>
     <cfRule type="duplicateValues" dxfId="11" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="27" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="28" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E360 E362:E494">
-    <cfRule type="duplicateValues" dxfId="7" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="34"/>
+  <conditionalFormatting sqref="E360 E362:E495">
+    <cfRule type="duplicateValues" dxfId="7" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="36" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="29"/>
     <cfRule type="duplicateValues" dxfId="1" priority="35" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="36" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
